--- a/testdata/configurationTST/data.xlsx
+++ b/testdata/configurationTST/data.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="113">
   <si>
     <t>username</t>
   </si>
@@ -302,127 +302,67 @@
     <t>205-9001000302715-60</t>
   </si>
   <si>
-    <t>Drre ĆEVMI</t>
-  </si>
-  <si>
-    <t>9032005130761</t>
-  </si>
-  <si>
-    <t>9032005664316</t>
-  </si>
-  <si>
-    <t>9032032922750</t>
+    <t>PETKO NOVAK</t>
+  </si>
+  <si>
+    <t>9032031803286</t>
+  </si>
+  <si>
+    <t>9032033386437</t>
+  </si>
+  <si>
+    <t>9011009710234</t>
+  </si>
+  <si>
+    <t>205-9001006224465-69</t>
+  </si>
+  <si>
+    <t>205-9001004175165-12</t>
+  </si>
+  <si>
+    <t>RS35 2059 0310 0048 9390 60</t>
+  </si>
+  <si>
+    <t>RS35 2059 0310 2550 7717 90</t>
+  </si>
+  <si>
+    <t>0049041360495</t>
+  </si>
+  <si>
+    <t>MILIJAN MILEN</t>
+  </si>
+  <si>
+    <t>Icer OVIVL</t>
+  </si>
+  <si>
+    <t>205900100417516512</t>
+  </si>
+  <si>
+    <t>OVIVL OSIR</t>
+  </si>
+  <si>
+    <t>Vklaragan OVIT</t>
+  </si>
+  <si>
+    <t>205-9001004906720-69</t>
+  </si>
+  <si>
+    <t>205900100490672069</t>
+  </si>
+  <si>
+    <t>STANIŠA NIKOLA</t>
+  </si>
+  <si>
+    <t>Jail ĆEVGIMILĆ</t>
   </si>
   <si>
     <t>205-9001001626239-86</t>
   </si>
   <si>
-    <t>205-9001007839862-95</t>
-  </si>
-  <si>
-    <t>205900100783986295</t>
-  </si>
-  <si>
-    <t>RS35 2059 0310 0000 1487 39</t>
-  </si>
-  <si>
-    <t>RS35 2059 0310 0001 9300 47</t>
-  </si>
-  <si>
-    <t>9011004938920</t>
-  </si>
-  <si>
-    <t>internal</t>
-  </si>
-  <si>
-    <t>4313 **** **** 5507</t>
-  </si>
-  <si>
-    <t>Visa Gold revolving</t>
-  </si>
-  <si>
-    <t>4176 **** **** 4784</t>
-  </si>
-  <si>
-    <t>0049015018282</t>
+    <t>0049018568496</t>
   </si>
   <si>
     <t>Stambeni kredit</t>
-  </si>
-  <si>
-    <t>0049038646620</t>
-  </si>
-  <si>
-    <t>ĆEVMI DRRE</t>
-  </si>
-  <si>
-    <t>DRRE ĆEVMI</t>
-  </si>
-  <si>
-    <t>Visa PayWave - ROZALIJA ČOLIĆ</t>
-  </si>
-  <si>
-    <t>4381********1044</t>
-  </si>
-  <si>
-    <t>Master standard - ZUZANA KARAN</t>
-  </si>
-  <si>
-    <t>5309********0724</t>
-  </si>
-  <si>
-    <t>PETKO NOVAK</t>
-  </si>
-  <si>
-    <t>9032031803286</t>
-  </si>
-  <si>
-    <t>9032033386437</t>
-  </si>
-  <si>
-    <t>9011009710234</t>
-  </si>
-  <si>
-    <t>205-9001006224465-69</t>
-  </si>
-  <si>
-    <t>205-9001004175165-12</t>
-  </si>
-  <si>
-    <t>RS35 2059 0310 0048 9390 60</t>
-  </si>
-  <si>
-    <t>RS35 2059 0310 2550 7717 90</t>
-  </si>
-  <si>
-    <t>0049041360495</t>
-  </si>
-  <si>
-    <t>Icer OVIVL</t>
-  </si>
-  <si>
-    <t>205900100417516512</t>
-  </si>
-  <si>
-    <t>OVIVL OSIR</t>
-  </si>
-  <si>
-    <t>Vklaragan OVIT</t>
-  </si>
-  <si>
-    <t>205-9001004906720-69</t>
-  </si>
-  <si>
-    <t>205900100490672069</t>
-  </si>
-  <si>
-    <t>STANIŠA NIKOLA</t>
-  </si>
-  <si>
-    <t>Jail ĆEVGIMILĆ</t>
-  </si>
-  <si>
-    <t>0049018568496</t>
   </si>
   <si>
     <t>0049005001233</t>
@@ -2035,17 +1975,17 @@
         <v>54</v>
       </c>
     </row>
-    <row r="5" customFormat="1" spans="1:44">
-      <c r="A5" t="s">
+    <row r="5" s="1" customFormat="1" spans="1:44">
+      <c r="A5" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="10" t="s">
         <v>45</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E5" s="12" t="s">
@@ -2087,47 +2027,47 @@
       <c r="Q5" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="R5" s="12" t="s">
+      <c r="R5" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="S5" s="8" t="s">
         <v>97</v>
-      </c>
-      <c r="S5" s="1" t="s">
-        <v>98</v>
       </c>
       <c r="T5" s="1" t="s">
         <v>59</v>
       </c>
       <c r="U5" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="V5" s="12" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="W5" s="1" t="s">
         <v>62</v>
       </c>
       <c r="X5" s="1" t="s">
-        <v>101</v>
+        <v>54</v>
       </c>
       <c r="Y5" s="1" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="Z5" s="1" t="s">
-        <v>102</v>
+        <v>54</v>
       </c>
       <c r="AA5" s="1" t="s">
-        <v>103</v>
+        <v>54</v>
       </c>
       <c r="AB5" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="AC5" s="12" t="s">
-        <v>105</v>
+        <v>54</v>
+      </c>
+      <c r="AC5" s="17" t="s">
+        <v>99</v>
       </c>
       <c r="AD5" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="AE5" s="12" t="s">
-        <v>107</v>
+        <v>69</v>
+      </c>
+      <c r="AE5" s="17" t="s">
+        <v>99</v>
       </c>
       <c r="AF5" s="1" t="s">
         <v>69</v>
@@ -2138,40 +2078,40 @@
       <c r="AH5" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="AI5" s="15" t="s">
-        <v>73</v>
+      <c r="AI5" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="AJ5" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="AK5" s="15" t="s">
-        <v>75</v>
+      <c r="AK5" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="AL5" s="1" t="s">
         <v>54</v>
       </c>
       <c r="AM5" s="1" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="AN5" s="1" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="AO5" t="s">
-        <v>110</v>
+        <v>54</v>
       </c>
       <c r="AP5" t="s">
-        <v>111</v>
+        <v>54</v>
       </c>
       <c r="AQ5" t="s">
-        <v>112</v>
+        <v>54</v>
       </c>
       <c r="AR5" t="s">
-        <v>113</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:44">
       <c r="A6" s="1" t="s">
-        <v>114</v>
+        <v>91</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>45</v>
@@ -2183,19 +2123,19 @@
         <v>47</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>115</v>
+        <v>92</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>49</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>116</v>
+        <v>93</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>49</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>117</v>
+        <v>94</v>
       </c>
       <c r="J6" s="1" t="s">
         <v>49</v>
@@ -2213,28 +2153,28 @@
         <v>55</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="P6" s="1" t="s">
         <v>55</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="R6" s="1" t="s">
         <v>54</v>
       </c>
       <c r="S6" s="8" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="T6" s="1" t="s">
         <v>59</v>
       </c>
       <c r="U6" s="1" t="s">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="V6" s="12" t="s">
-        <v>117</v>
+        <v>94</v>
       </c>
       <c r="W6" s="1" t="s">
         <v>62</v>
@@ -2255,13 +2195,13 @@
         <v>54</v>
       </c>
       <c r="AC6" s="17" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="AD6" s="1" t="s">
         <v>69</v>
       </c>
       <c r="AE6" s="17" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="AF6" s="1" t="s">
         <v>69</v>
@@ -2285,10 +2225,10 @@
         <v>54</v>
       </c>
       <c r="AM6" s="1" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="AN6" s="1" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="AO6" t="s">
         <v>54</v>
@@ -2305,7 +2245,7 @@
     </row>
     <row r="7" customFormat="1" spans="1:44">
       <c r="A7" t="s">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>45</v>
@@ -2347,7 +2287,7 @@
         <v>54</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="P7" s="1" t="s">
         <v>54</v>
@@ -2356,7 +2296,7 @@
         <v>54</v>
       </c>
       <c r="R7" s="12" t="s">
-        <v>124</v>
+        <v>102</v>
       </c>
       <c r="S7" s="1" t="s">
         <v>54</v>
@@ -2419,10 +2359,10 @@
         <v>54</v>
       </c>
       <c r="AM7" s="1" t="s">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="AN7" s="1" t="s">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="AO7" t="s">
         <v>54</v>
@@ -2439,7 +2379,7 @@
     </row>
     <row r="8" customFormat="1" spans="1:44">
       <c r="A8" t="s">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="B8" s="10" t="s">
         <v>45</v>
@@ -2481,7 +2421,7 @@
         <v>54</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="P8" s="1" t="s">
         <v>54</v>
@@ -2490,7 +2430,7 @@
         <v>54</v>
       </c>
       <c r="R8" s="12" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="S8" s="1" t="s">
         <v>54</v>
@@ -2553,10 +2493,10 @@
         <v>54</v>
       </c>
       <c r="AM8" s="1" t="s">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="AN8" s="1" t="s">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="AO8" t="s">
         <v>54</v>
@@ -2573,7 +2513,7 @@
     </row>
     <row r="9" s="1" customFormat="1" spans="1:44">
       <c r="A9" s="1" t="s">
-        <v>130</v>
+        <v>108</v>
       </c>
       <c r="B9" s="10" t="s">
         <v>45</v>
@@ -2615,7 +2555,7 @@
         <v>55</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="P9" s="1" t="s">
         <v>54</v>
@@ -2654,13 +2594,13 @@
         <v>54</v>
       </c>
       <c r="AC9" s="12" t="s">
-        <v>131</v>
+        <v>110</v>
       </c>
       <c r="AD9" s="1" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="AE9" s="12" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="AF9" s="1" t="s">
         <v>69</v>
@@ -2707,11 +2647,11 @@
     <hyperlink ref="B2" r:id="rId1" display="https://uat.dbp.nlb.si/web-retail/login" tooltip="https://uat.dbp.nlb.si/web-retail/login"/>
     <hyperlink ref="B3" r:id="rId1" display="https://uat.dbp.nlb.si/web-retail/login" tooltip="https://uat.dbp.nlb.si/web-retail/login"/>
     <hyperlink ref="B4" r:id="rId1" display="https://uat.dbp.nlb.si/web-retail/login" tooltip="https://uat.dbp.nlb.si/web-retail/login"/>
-    <hyperlink ref="B5" r:id="rId1" display="https://uat.dbp.nlb.si/web-retail/login" tooltip="https://uat.dbp.nlb.si/web-retail/login"/>
     <hyperlink ref="B6" r:id="rId1" display="https://uat.dbp.nlb.si/web-retail/login" tooltip="https://uat.dbp.nlb.si/web-retail/login"/>
     <hyperlink ref="B7" r:id="rId1" display="https://uat.dbp.nlb.si/web-retail/login" tooltip="https://uat.dbp.nlb.si/web-retail/login"/>
     <hyperlink ref="B8" r:id="rId1" display="https://uat.dbp.nlb.si/web-retail/login" tooltip="https://uat.dbp.nlb.si/web-retail/login"/>
     <hyperlink ref="B9" r:id="rId1" display="https://uat.dbp.nlb.si/web-retail/login" tooltip="https://uat.dbp.nlb.si/web-retail/login"/>
+    <hyperlink ref="B5" r:id="rId1" display="https://uat.dbp.nlb.si/web-retail/login" tooltip="https://uat.dbp.nlb.si/web-retail/login"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
